--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47D987F-8169-4859-AA70-A9BA3B29EC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C0F2EB-58C8-4D8C-9B20-BF8F934D161A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,10 +111,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Sing-song Wanderer</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>咏永的彷徨者</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -136,6 +132,10 @@
   </si>
   <si>
     <t>Errante que Arde en Silencio</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sing-Song Wanderer</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -542,13 +542,13 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" t="s">
         <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
@@ -603,19 +603,19 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:10">

--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C0F2EB-58C8-4D8C-9B20-BF8F934D161A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A2C15E-0B07-40FE-9B9C-530DF38C1F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -617,6 +617,15 @@
       <c r="G5" t="s">
         <v>22</v>
       </c>
+      <c r="H5">
+        <v>27</v>
+      </c>
+      <c r="I5">
+        <v>28</v>
+      </c>
+      <c r="J5">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">

--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A2C15E-0B07-40FE-9B9C-530DF38C1F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C64B8C-042A-4B1E-B49E-DD81DAC29875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -137,6 +137,18 @@
   <si>
     <t>Sing-Song Wanderer</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>nameRussian</t>
+  </si>
+  <si>
+    <t>Скиталец, вскипающий от тишины</t>
+  </si>
+  <si>
+    <t>Пленительная Скиталица забвения</t>
+  </si>
+  <si>
+    <t>Поющий Скиталец</t>
   </si>
 </sst>
 </file>
@@ -482,19 +494,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="21.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="18.875" customWidth="1"/>
     <col min="5" max="7" width="27.25" customWidth="1"/>
-    <col min="8" max="8" width="8.625" customWidth="1"/>
-    <col min="9" max="9" width="7.875" customWidth="1"/>
-    <col min="10" max="10" width="13.375" customWidth="1"/>
+    <col min="8" max="8" width="62" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.625" customWidth="1"/>
+    <col min="10" max="10" width="7.875" customWidth="1"/>
+    <col min="11" max="11" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -517,21 +530,24 @@
         <v>16</v>
       </c>
       <c r="H1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="93.75">
+    <row r="3" spans="1:11" ht="93.75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -553,17 +569,20 @@
       <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3">
         <v>7</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>8</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="93.75">
+    <row r="4" spans="1:11" ht="93.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -585,17 +604,20 @@
       <c r="G4" t="s">
         <v>18</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4">
         <v>17</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>18</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="75">
+    <row r="5" spans="1:11" ht="75">
       <c r="A5">
         <v>3</v>
       </c>
@@ -617,47 +639,50 @@
       <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5">
         <v>27</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>28</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C64B8C-042A-4B1E-B49E-DD81DAC29875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836FAAA1-3D28-4FF1-9C44-EBF2080D62FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -149,6 +149,18 @@
   </si>
   <si>
     <t>Поющий Скиталец</t>
+  </si>
+  <si>
+    <t>nameGerman</t>
+  </si>
+  <si>
+    <t>Der in der Stille Entbrennende</t>
+  </si>
+  <si>
+    <t>Die Betörende des Vergessens</t>
+  </si>
+  <si>
+    <t>Der singende Umherirrende</t>
   </si>
 </sst>
 </file>
@@ -494,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="21.75" style="1" customWidth="1"/>
@@ -502,12 +514,13 @@
     <col min="4" max="4" width="18.875" customWidth="1"/>
     <col min="5" max="7" width="27.25" customWidth="1"/>
     <col min="8" max="8" width="62" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.625" customWidth="1"/>
-    <col min="10" max="10" width="7.875" customWidth="1"/>
-    <col min="11" max="11" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.625" customWidth="1"/>
+    <col min="11" max="11" width="7.875" customWidth="1"/>
+    <col min="12" max="12" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -533,21 +546,24 @@
         <v>27</v>
       </c>
       <c r="I1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="93.75">
+    <row r="3" spans="1:12" ht="93.75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -572,17 +588,20 @@
       <c r="H3" t="s">
         <v>28</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3">
         <v>7</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>8</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="93.75">
+    <row r="4" spans="1:12" ht="93.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -607,17 +626,20 @@
       <c r="H4" t="s">
         <v>29</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4">
         <v>17</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>18</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="75">
+    <row r="5" spans="1:12" ht="75">
       <c r="A5">
         <v>3</v>
       </c>
@@ -642,47 +664,50 @@
       <c r="H5" t="s">
         <v>30</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5">
         <v>27</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>28</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836FAAA1-3D28-4FF1-9C44-EBF2080D62FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA017DE-3672-4696-AACE-BFE3DE52D927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -161,6 +161,18 @@
   </si>
   <si>
     <t>Der singende Umherirrende</t>
+  </si>
+  <si>
+    <t>nameFrench</t>
+  </si>
+  <si>
+    <t>L'Errant qui s'embrase dans le silence</t>
+  </si>
+  <si>
+    <t>L'Envoûtante de l'oubli</t>
+  </si>
+  <si>
+    <t>L'Errant qui chante</t>
   </si>
 </sst>
 </file>
@@ -506,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="21.75" style="1" customWidth="1"/>
@@ -515,12 +527,13 @@
     <col min="5" max="7" width="27.25" customWidth="1"/>
     <col min="8" max="8" width="62" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.625" customWidth="1"/>
-    <col min="11" max="11" width="7.875" customWidth="1"/>
-    <col min="12" max="12" width="13.375" customWidth="1"/>
+    <col min="10" max="10" width="29.625" customWidth="1"/>
+    <col min="11" max="11" width="8.625" customWidth="1"/>
+    <col min="12" max="12" width="7.875" customWidth="1"/>
+    <col min="13" max="13" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -549,21 +562,24 @@
         <v>31</v>
       </c>
       <c r="J1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="93.75">
+    <row r="3" spans="1:13" ht="93.75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -591,17 +607,20 @@
       <c r="I3" t="s">
         <v>32</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3">
         <v>7</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>8</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="93.75">
+    <row r="4" spans="1:13" ht="93.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -629,17 +648,20 @@
       <c r="I4" t="s">
         <v>33</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4">
         <v>17</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>18</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="75">
+    <row r="5" spans="1:13" ht="75">
       <c r="A5">
         <v>3</v>
       </c>
@@ -667,47 +689,50 @@
       <c r="I5" t="s">
         <v>34</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5">
         <v>27</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>28</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA017DE-3672-4696-AACE-BFE3DE52D927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A386B68C-60AA-42BA-AFF1-D9980042A1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -173,6 +173,18 @@
   </si>
   <si>
     <t>L'Errant qui chante</t>
+  </si>
+  <si>
+    <t>nameTurkish</t>
+  </si>
+  <si>
+    <t>Sessizlikte Kızışan Gezgin</t>
+  </si>
+  <si>
+    <t>Unutuşun Büyüleyici Gezgini</t>
+  </si>
+  <si>
+    <t>Şarkı Söyleyen Gezgin</t>
   </si>
 </sst>
 </file>
@@ -518,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="21.75" style="1" customWidth="1"/>
@@ -528,12 +540,13 @@
     <col min="8" max="8" width="62" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="29.625" customWidth="1"/>
-    <col min="11" max="11" width="8.625" customWidth="1"/>
-    <col min="12" max="12" width="7.875" customWidth="1"/>
-    <col min="13" max="13" width="13.375" customWidth="1"/>
+    <col min="11" max="11" width="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.625" customWidth="1"/>
+    <col min="13" max="13" width="7.875" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -565,21 +578,24 @@
         <v>35</v>
       </c>
       <c r="K1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="93.75">
+    <row r="3" spans="1:14" ht="93.75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -610,17 +626,20 @@
       <c r="J3" t="s">
         <v>36</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3">
         <v>7</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>8</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="93.75">
+    <row r="4" spans="1:14" ht="93.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -651,17 +670,20 @@
       <c r="J4" t="s">
         <v>37</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4">
         <v>17</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>18</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="75">
+    <row r="5" spans="1:14" ht="75">
       <c r="A5">
         <v>3</v>
       </c>
@@ -692,47 +714,50 @@
       <c r="J5" t="s">
         <v>38</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5">
         <v>27</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>28</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>10</v>
       </c>
